--- a/tasklist/interstellerhuck.xlsx
+++ b/tasklist/interstellerhuck.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t>課題ID</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>滞空状態でのHe3回収・圧縮</t>
+  </si>
+  <si>
+    <t>26.05.16</t>
   </si>
   <si>
     <t>（ラムジェット代替）。</t>
@@ -4021,7 +4024,8 @@
     <col customWidth="0" min="2" max="3" style="1" width="12.630000000000001"/>
     <col customWidth="1" min="4" max="4" style="1" width="9.7109375"/>
     <col customWidth="1" min="5" max="5" style="1" width="15.44"/>
-    <col customWidth="0" min="6" max="16384" style="1" width="12.630000000000001"/>
+    <col customWidth="1" min="6" max="6" style="1" width="14.00390625"/>
+    <col customWidth="0" min="7" max="16384" style="1" width="12.630000000000001"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5">
@@ -4377,11 +4381,15 @@
       <c r="C10" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -32152,13 +32160,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>24</v>
@@ -32171,16 +32179,16 @@
         <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>8</v>
@@ -32189,42 +32197,42 @@
     </row>
     <row r="3" ht="76.5">
       <c r="A3" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" ht="38.25">
       <c r="A4" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>8</v>
@@ -32233,35 +32241,35 @@
     </row>
     <row r="5" ht="38.25">
       <c r="A5" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" ht="63.75">
       <c r="A6" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>8</v>
@@ -32269,17 +32277,17 @@
     </row>
     <row r="7" ht="38.25">
       <c r="A7" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>8</v>
@@ -32288,36 +32296,36 @@
     </row>
     <row r="8" ht="51">
       <c r="A8" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G8" s="2"/>
     </row>
     <row r="9" ht="38.25">
       <c r="A9" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>8</v>
@@ -32326,17 +32334,17 @@
     </row>
     <row r="10" ht="38.25">
       <c r="A10" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>8</v>
@@ -32345,52 +32353,52 @@
     </row>
     <row r="11" ht="38.25">
       <c r="A11" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" ht="15.75">
       <c r="A12" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" ht="76.5">
       <c r="A13" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
